--- a/assets/downloads/nis2-auditi-toendite-mall.xlsx
+++ b/assets/downloads/nis2-auditi-toendite-mall.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Juhend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tõendid'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tõendid'!$A$1:$M$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Tõendid'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -583,12 +583,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
@@ -668,10 +668,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="49" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>(a)</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -681,12 +681,12 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Riskianalüüs ja turvapoliitika</t>
+          <t>Riskianalüüs ja infosüsteemide turvalisuse poliitika</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Kinnitatud riskiregister ja turvapoliitika</t>
+          <t>Kinnitatud riskiregister, turvapoliitika ja riskianalüüsi metoodika (versioon, kinnitaja, kuupäev)</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Vali 3 riski ja kontrolli ravi ning jääkriski</t>
+          <t>Vali 3 riski; kontrolli ravi, omanikku ja jääkriski</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -715,10 +715,10 @@
       </c>
       <c r="M2" s="4" t="n"/>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="79" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>(b)</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Intsidendiprotseduur ja kontaktid</t>
+          <t>Intsidendiprotseduur, kontaktid ja teavituste logi; esmane teade hiljemalt 24 h, intsidenditeade hiljemalt 72 h, lõpparuanne ühe kuu jooksul intsidenditeate esitamisest (KüTS § 8)</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>Simuleeri intsident ja kontrolli 24/72 tunni rada</t>
+          <t>Kontrolli, kas protseduur sisaldab 24 h, 72 h ja lõpparuande tähtaegu ning rolle; vaata viimast teavituste logi</t>
         </is>
       </c>
       <c r="G3" s="8" t="n"/>
@@ -765,7 +765,7 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>(c)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -775,12 +775,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Toimepidevus ja varundus</t>
+          <t>Toimepidevus, varukoopiate haldus ja taastamine ning kriisijuhtimine</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Varundusplaan ja taastetesti raport</t>
+          <t>Varundusplaan, viimase taastetesti raport, RTO/RPO ja kriisijuhtimise kord</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -809,10 +809,10 @@
       </c>
       <c r="M4" s="4" t="n"/>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>(d)</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Tarneahela turve</t>
+          <t>Tarneahela turvalisus</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Kriitiliste tarnijate nimekiri ja lepingud</t>
+          <t>Kriitiliste tarnijate nimekiri, lepingute turvatingimused ja hindamise märkmed (sh suhted otseste tarnijate ja teenuseosutajatega)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Vali 3 tarnijat ja kontrolli due diligence't</t>
+          <t>Vali 3 tarnijat ja kontrolli lepingut ning hindamist</t>
         </is>
       </c>
       <c r="G5" s="8" t="n"/>
@@ -856,10 +856,10 @@
       </c>
       <c r="M5" s="7" t="n"/>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="49" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>(e)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Turvaline arendus ja haavatavused</t>
+          <t>Turvalisus hankimisel, arendamisel ja hooldamisel</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Haavatavuste protsess ja parandusajad</t>
+          <t>Haavatavuste käsitlemise ja avalikustamise kord, kanal ja parandamise logi (tähtajad on sisemised sihid)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Kontrolli 5 haavatavuse parandamise tõendit</t>
+          <t>Kontrolli 5 viimase haavatavuse parandamise tõendit</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -903,10 +903,10 @@
       </c>
       <c r="M6" s="4" t="n"/>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="49" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>(f)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Tõhususe testimine</t>
+          <t>Riskijuhtimismeetmete tõhususe hindamine</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Testiplaan ja viimased tulemused</t>
+          <t>Testiplaan, viimased tulemused ja leidude jälgimine</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Kontrolli, kas testid katavad kriitilised süsteemid</t>
+          <t>Kontrolli, kas testid katavad kriitilised süsteemid ja kas leiud on parandatud</t>
         </is>
       </c>
       <c r="G7" s="8" t="n"/>
@@ -953,7 +953,7 @@
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>(g)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Küberhügieen ja koolitus</t>
+          <t>Küberhügieen ja küberturvalisuse koolitus</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Koolituskava ja osalemise tõendid</t>
+          <t>Koolituskava, osalejate nimekiri ja sisu ajakohasus</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -997,10 +997,10 @@
       </c>
       <c r="M8" s="4" t="n"/>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="49" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>(h)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Krüpteerimine</t>
+          <t>Krüptograafia ja krüpteerimine</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Krüpteerimise poliitika ja kasutuspõhimõtted</t>
+          <t>Krüptograafia ja krüpteerimise poliitika, võtmete ja sertifikaatide loetelu</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Kontrolli andmete liikumist ja krüpteerimist</t>
+          <t>Kontrolli andmete liikumist, krüpteerimist ja sertifikaatide aegumist</t>
         </is>
       </c>
       <c r="G9" s="8" t="n"/>
@@ -1047,7 +1047,7 @@
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>(i)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Ligipääsukontroll</t>
+          <t>Personaliturvalisus, juurdepääsukontroll ja varahaldus</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Privileegide maatriks ja ülevaatuse tõendid</t>
+          <t>Õiguste maatriks ja ülevaatuse tõend, töölt lahkumise kord, varanimekiri</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>IT-juht</t>
+          <t>IT-juht ja personal</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Vali 5 kontot ja kontrolli õigusi</t>
+          <t>Vali 5 kontot (sh 1 lahkunud töötaja) ja kontrolli õigusi ning varakirjeid</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -1091,10 +1091,10 @@
       </c>
       <c r="M10" s="4" t="n"/>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="49" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>(j)</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>MFA ja turvaline side</t>
+          <t>Mitmefaktorautentimine ja turvaline side (sh hädaolukorra side)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>MFA katvus ja erisused</t>
+          <t>MFA katvuse loend kriitiliste kontodega, turvalise side kirjeldus ja hädaolukorra sideviis</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Kontrolli kriitiliste kontode MFA-d</t>
+          <t>Kontrolli kriitiliste kontode MFA-d ja hädaolukorra sideviisi toimimist</t>
         </is>
       </c>
       <c r="G11" s="8" t="n"/>
@@ -1138,8 +1138,55 @@
       </c>
       <c r="M11" s="7" t="n"/>
     </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Juhtorgan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>art 20 · KüTS §6¹</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Juhtorgani kohustused (art 20 / KüTS §6¹)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Juhatuse protokoll, mis kinnitab riskijuhtimismeetmed; koolituse tõend</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Juhatus</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Kontrolli viimast juhatuse protokolli ja koolituse tõendit</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Pole hinnatud</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Pole alustatud</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M12"/>
   <conditionalFormatting sqref="H2:H200">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$H2="Vastab"</formula>
@@ -1211,7 +1258,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Töömall tõendite kogumiseks NIS2 direktiivi (EL) 2022/2555 artikli 21 lõike 2 kümne miinimumnõude kohta. Täida lehel „Tõendid“ üks rida iga meetme kohta.</t>
+          <t>Töömall tõendite kogumiseks NIS2 direktiivi (EL) 2022/2555 artikli 21 lõike 2 punktide (a)–(j) ja artikli 20 juhtorgani kohustuste kohta. Täida lehel „Tõendid“ üks rida iga punkti ja juhtorgani rea kohta.</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1344,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>NIS2 artikli 21 lõike 2 punkt; hoiab rea seotud direktiivi tekstiga.</t>
+          <t>Artikli 21 lõike 2 punkt (a)–(j) või juhtorgani rida (art 20); hoiab rea seotud direktiivi tekstiga.</t>
         </is>
       </c>
     </row>
@@ -1477,14 +1524,14 @@
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>See on töövahend, mitte auditiraport, sertifikaat ega vastavusdeklaratsioon. NIS2 ei nõua ühte sertifikaati: auditi järeldus peab põhinema ulatusel, kriteeriumidel ja nähtud tõenditel. Täidetud tabel ilma tõendite asukohtadeta ei ole auditiks piisav. Kontrolli enne kasutamist kehtivat NIS2/Eesti KüTS redaktsiooni.</t>
+          <t>See on töövahend, mitte auditiraport, sertifikaat ega vastavusdeklaratsioon. NIS2 ei nõua ühte sertifikaati: auditi järeldus peab põhinema ulatusel, kriteeriumidel ja nähtud tõenditel. Täidetud tabel ilma tõendite asukohtadeta ei ole auditiks piisav. Kontrolli enne kasutamist kehtivat KüTS-i redaktsiooni (kehtiv 16.10.2026).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>Allikas: NIS2 direktiiv (EL) 2022/2555, art 21 lg 2 · tehisabiline.ee/nis2/audit/</t>
+          <t>Allikas: NIS2 direktiiv (EL) 2022/2555, art 20 ja art 21 lg 2 · KüTS (kehtiv 16.10.2026) · tehisabiline.ee/nis2/audit/</t>
         </is>
       </c>
     </row>
